--- a/artfynd/A 11183-2024 artfynd.xlsx
+++ b/artfynd/A 11183-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131711428</v>
       </c>
       <c r="B2" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131711331</v>
       </c>
       <c r="B3" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131711067</v>
       </c>
       <c r="B4" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131711351</v>
       </c>
       <c r="B7" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>131710790</v>
       </c>
       <c r="B11" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11183-2024 artfynd.xlsx
+++ b/artfynd/A 11183-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131711428</v>
       </c>
       <c r="B2" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131711331</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131711067</v>
       </c>
       <c r="B4" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131711275</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131711300</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131711351</v>
       </c>
       <c r="B7" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>131711389</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>131711015</v>
       </c>
       <c r="B9" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>131710941</v>
       </c>
       <c r="B10" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>131710790</v>
       </c>
       <c r="B11" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11183-2024 artfynd.xlsx
+++ b/artfynd/A 11183-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131711428</v>
       </c>
       <c r="B2" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131711331</v>
       </c>
       <c r="B3" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131711067</v>
       </c>
       <c r="B4" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131711275</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131711300</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131711351</v>
       </c>
       <c r="B7" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>131711389</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>131711015</v>
       </c>
       <c r="B9" t="n">
-        <v>91850</v>
+        <v>91853</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>131710941</v>
       </c>
       <c r="B10" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>131710790</v>
       </c>
       <c r="B11" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 11183-2024 artfynd.xlsx
+++ b/artfynd/A 11183-2024 artfynd.xlsx
@@ -1538,42 +1538,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131710941</v>
+        <v>131710790</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588935</v>
+        <v>589055</v>
       </c>
       <c r="R10" t="n">
-        <v>6423310</v>
+        <v>6423334</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,17 +1619,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I asp</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1648,42 +1644,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131710790</v>
+        <v>131710941</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1691,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589055</v>
+        <v>588935</v>
       </c>
       <c r="R11" t="n">
-        <v>6423334</v>
+        <v>6423310</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,13 +1725,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I asp</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11183-2024 artfynd.xlsx
+++ b/artfynd/A 11183-2024 artfynd.xlsx
@@ -1538,42 +1538,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131710790</v>
+        <v>131710941</v>
       </c>
       <c r="B10" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589055</v>
+        <v>588935</v>
       </c>
       <c r="R10" t="n">
-        <v>6423334</v>
+        <v>6423310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,13 +1619,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I asp</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1644,42 +1648,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131710941</v>
+        <v>131710790</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1687,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588935</v>
+        <v>589055</v>
       </c>
       <c r="R11" t="n">
-        <v>6423310</v>
+        <v>6423334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,17 +1729,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>I asp</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11183-2024 artfynd.xlsx
+++ b/artfynd/A 11183-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131711428</v>
       </c>
       <c r="B2" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>131711331</v>
       </c>
       <c r="B3" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131711067</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>131711275</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>131711300</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>131711351</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>131711389</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>131711015</v>
       </c>
       <c r="B9" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,42 +1538,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131710941</v>
+        <v>131710790</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>99044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588935</v>
+        <v>589055</v>
       </c>
       <c r="R10" t="n">
-        <v>6423310</v>
+        <v>6423334</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,17 +1619,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I asp</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1648,42 +1644,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131710790</v>
+        <v>131710941</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1691,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589055</v>
+        <v>588935</v>
       </c>
       <c r="R11" t="n">
-        <v>6423334</v>
+        <v>6423310</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,13 +1725,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I asp</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11183-2024 artfynd.xlsx
+++ b/artfynd/A 11183-2024 artfynd.xlsx
@@ -1538,42 +1538,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131710790</v>
+        <v>131710941</v>
       </c>
       <c r="B10" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589055</v>
+        <v>588935</v>
       </c>
       <c r="R10" t="n">
-        <v>6423334</v>
+        <v>6423310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,13 +1619,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I asp</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1644,42 +1648,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131710941</v>
+        <v>131710790</v>
       </c>
       <c r="B11" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1687,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588935</v>
+        <v>589055</v>
       </c>
       <c r="R11" t="n">
-        <v>6423310</v>
+        <v>6423334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,17 +1729,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>I asp</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11183-2024 artfynd.xlsx
+++ b/artfynd/A 11183-2024 artfynd.xlsx
@@ -1538,42 +1538,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131710941</v>
+        <v>131710790</v>
       </c>
       <c r="B10" t="n">
-        <v>57901</v>
+        <v>99044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588935</v>
+        <v>589055</v>
       </c>
       <c r="R10" t="n">
-        <v>6423310</v>
+        <v>6423334</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,17 +1619,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I asp</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1648,42 +1644,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131710790</v>
+        <v>131710941</v>
       </c>
       <c r="B11" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1691,10 +1687,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589055</v>
+        <v>588935</v>
       </c>
       <c r="R11" t="n">
-        <v>6423334</v>
+        <v>6423310</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,13 +1725,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I asp</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11183-2024 artfynd.xlsx
+++ b/artfynd/A 11183-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131711428</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131711067</v>
+        <v>131711331</v>
       </c>
       <c r="B3" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588831</v>
+        <v>588775</v>
       </c>
       <c r="R3" t="n">
-        <v>6423374</v>
+        <v>6423407</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131711331</v>
+        <v>131711067</v>
       </c>
       <c r="B4" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588775</v>
+        <v>588831</v>
       </c>
       <c r="R4" t="n">
-        <v>6423407</v>
+        <v>6423374</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1216,7 +1216,7 @@
         <v>131711351</v>
       </c>
       <c r="B7" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>131711015</v>
       </c>
       <c r="B9" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1538,42 +1538,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131710790</v>
+        <v>131710941</v>
       </c>
       <c r="B10" t="n">
-        <v>99095</v>
+        <v>57945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589055</v>
+        <v>588935</v>
       </c>
       <c r="R10" t="n">
-        <v>6423334</v>
+        <v>6423310</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,13 +1619,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>I asp</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1644,42 +1648,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131710941</v>
+        <v>131710790</v>
       </c>
       <c r="B11" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1687,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588935</v>
+        <v>589055</v>
       </c>
       <c r="R11" t="n">
-        <v>6423310</v>
+        <v>6423334</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,17 +1729,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>I asp</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11183-2024 artfynd.xlsx
+++ b/artfynd/A 11183-2024 artfynd.xlsx
@@ -675,42 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131711428</v>
+        <v>131711015</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>91995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589081</v>
+        <v>588889</v>
       </c>
       <c r="R2" t="n">
-        <v>6423336</v>
+        <v>6423355</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,42 +784,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131711331</v>
+        <v>131710941</v>
       </c>
       <c r="B3" t="n">
-        <v>99098</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588775</v>
+        <v>588935</v>
       </c>
       <c r="R3" t="n">
-        <v>6423407</v>
+        <v>6423310</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,13 +865,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I asp</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,42 +894,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131711067</v>
+        <v>131711275</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -930,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588831</v>
+        <v>588813</v>
       </c>
       <c r="R4" t="n">
-        <v>6423374</v>
+        <v>6423367</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,13 +975,17 @@
           <t>2026-03-17</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I asp</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -993,14 +1004,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131711275</v>
+        <v>131711300</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588813</v>
+        <v>588805</v>
       </c>
       <c r="R5" t="n">
-        <v>6423367</v>
+        <v>6423374</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,14 +1114,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131711300</v>
+        <v>131711389</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1146,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588805</v>
+        <v>588913</v>
       </c>
       <c r="R6" t="n">
-        <v>6423374</v>
+        <v>6423370</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131711351</v>
+        <v>131710790</v>
       </c>
       <c r="B7" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588721</v>
+        <v>589055</v>
       </c>
       <c r="R7" t="n">
-        <v>6423416</v>
+        <v>6423334</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,42 +1330,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131711389</v>
+        <v>131711067</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>99195</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1362,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588913</v>
+        <v>588831</v>
       </c>
       <c r="R8" t="n">
-        <v>6423370</v>
+        <v>6423374</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,17 +1411,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>I asp</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1429,45 +1436,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131711015</v>
+        <v>131711331</v>
       </c>
       <c r="B9" t="n">
-        <v>91913</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1475,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588889</v>
+        <v>588775</v>
       </c>
       <c r="R9" t="n">
-        <v>6423355</v>
+        <v>6423407</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1538,42 +1542,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131710941</v>
+        <v>131711351</v>
       </c>
       <c r="B10" t="n">
-        <v>57945</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1581,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588935</v>
+        <v>588721</v>
       </c>
       <c r="R10" t="n">
-        <v>6423310</v>
+        <v>6423416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1619,17 +1623,13 @@
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>I asp</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131710790</v>
+        <v>131711428</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589055</v>
+        <v>589081</v>
       </c>
       <c r="R11" t="n">
-        <v>6423334</v>
+        <v>6423336</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
